--- a/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,28 +526,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>102</v>
       </c>
     </row>
@@ -545,28 +557,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>140</v>
       </c>
     </row>
@@ -576,28 +588,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>35</v>
       </c>
     </row>
@@ -607,28 +619,28 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>43907</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>440</v>
       </c>
     </row>
@@ -638,28 +650,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -669,34 +681,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0.1010785350953814</v>
-      </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="6" t="n">
+        <v>0.1010785350953813</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>85059</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -706,28 +718,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>1170</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>390</v>
       </c>
     </row>
@@ -737,34 +749,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="4" t="n">
         <v>2.35</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>76.2</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>0.2620449311218541</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>49170</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>1463</v>
       </c>
     </row>
@@ -774,28 +786,28 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>1623</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>677</v>
       </c>
     </row>
@@ -805,28 +817,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -836,28 +848,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -867,28 +879,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>971</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>433</v>
       </c>
     </row>
@@ -898,28 +910,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
         <v>26346</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -929,28 +941,28 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="4" t="n">
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
         <v>80.7</v>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="3" t="n">
         <v>57649</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>6553</v>
       </c>
     </row>
@@ -960,34 +972,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>265.07</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="6" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>36604</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -997,28 +1009,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="B17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="3" t="n">
         <v>217937</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1028,34 +1040,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>2.045420729252858e-05</v>
-      </c>
-      <c r="J18" s="2" t="n">
+      <c r="I18" s="6" t="n">
+        <v>2.045420729252859e-05</v>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>1057923</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1065,28 +1077,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>652</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>244</v>
       </c>
     </row>
@@ -1096,28 +1108,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1127,34 +1139,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>85.8</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>0.08361480732068774</v>
-      </c>
-      <c r="J21" s="2" t="n">
+      <c r="I21" s="6" t="n">
+        <v>0.08361480732068771</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>264478</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>15275</v>
       </c>
     </row>
@@ -1164,28 +1176,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
         <v>656</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1195,28 +1207,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="B23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="3" t="n">
         <v>1455</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1226,34 +1238,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>67.2</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>0.0627367499128533</v>
-      </c>
-      <c r="J24" s="2" t="n">
+      <c r="I24" s="6" t="n">
+        <v>0.06273674991285325</v>
+      </c>
+      <c r="J24" s="3" t="n">
         <v>93912</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>4718</v>
       </c>
     </row>
@@ -1263,28 +1275,28 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="B25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
+      <c r="E25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="3" t="n">
         <v>2745</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1294,28 +1306,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
+      <c r="E26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
         <v>2745</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1325,28 +1337,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>36499</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1356,34 +1368,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>80.7</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <v>0.8930041904516862</v>
-      </c>
-      <c r="J28" s="2" t="n">
+      <c r="I28" s="6" t="n">
+        <v>0.8930041904516861</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>68446</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>7637</v>
       </c>
     </row>
@@ -1393,34 +1405,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="5" t="n">
         <v>69.5</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>0.07495549929133034</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="I29" s="6" t="n">
+        <v>0.0749554992913304</v>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>282888</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>22602</v>
       </c>
     </row>
@@ -1430,34 +1442,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>62.4</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0.006170430008920979</v>
-      </c>
-      <c r="J30" s="2" t="n">
+      <c r="I30" s="6" t="n">
+        <v>0.006170430008920973</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>1155076</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1467,34 +1479,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0.1883996373295241</v>
-      </c>
-      <c r="J31" s="2" t="n">
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.188399637329524</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>80888</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1504,34 +1516,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.2443574036478494</v>
-      </c>
-      <c r="J32" s="2" t="n">
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.2443574036478493</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>70879</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1541,34 +1553,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="4" t="n">
         <v>2.45</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="I33" s="5" t="n">
-        <v>0.9409244606491106</v>
-      </c>
-      <c r="J33" s="2" t="n">
+      <c r="I33" s="6" t="n">
+        <v>0.9409244606491105</v>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>65550</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>6813</v>
       </c>
     </row>
@@ -1578,28 +1590,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="4" t="n">
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="n">
         <v>39.5</v>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
         <v>211318</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1609,28 +1621,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="n">
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="2" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>46667</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1640,28 +1652,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
+      <c r="B36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1671,34 +1683,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="n">
+      <c r="E37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="5" t="n">
         <v>42.9</v>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="I37" s="6" t="n">
         <v>0.07744276379719461</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="3" t="n">
         <v>972077</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1708,28 +1720,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>38308</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1739,28 +1751,28 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
+      <c r="B39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1770,28 +1782,28 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>430507</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>7761</v>
       </c>
     </row>
@@ -1801,28 +1813,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="3" t="n">
+      <c r="B41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
         <v>47867</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -1832,34 +1844,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>0.1162788351325631</v>
-      </c>
-      <c r="J42" s="2" t="n">
+      <c r="I42" s="6" t="n">
+        <v>0.116278835132563</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>270107</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>13301</v>
       </c>
     </row>
@@ -1869,28 +1881,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="3" t="n">
+      <c r="B43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>72784</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>1408</v>
       </c>
     </row>
@@ -1900,28 +1912,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="3" t="n">
+      <c r="B44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1931,28 +1943,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="n">
+      <c r="B45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="3" t="n">
         <v>150671</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -1962,28 +1974,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="n">
+      <c r="B46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>159482</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -1993,28 +2005,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="3" t="n">
         <v>109557</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2024,34 +2036,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F48" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="H48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="n">
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="3" t="n">
         <v>900752</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K48" s="3" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2061,28 +2073,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3" t="n">
+      <c r="B49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="K49" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2092,34 +2104,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="3" t="n">
+      <c r="C50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="5" t="n">
         <v>76.5</v>
       </c>
-      <c r="I50" s="5" t="n">
-        <v>0.6025874689662089</v>
-      </c>
-      <c r="J50" s="2" t="n">
+      <c r="I50" s="6" t="n">
+        <v>0.6025874689662087</v>
+      </c>
+      <c r="J50" s="3" t="n">
         <v>271067</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="K50" s="3" t="n">
         <v>17634</v>
       </c>
     </row>
@@ -2129,28 +2141,28 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="3" t="n">
+      <c r="B51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K51" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2160,28 +2172,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="3" t="n">
+      <c r="B52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="3" t="n">
         <v>142239</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K52" s="3" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2191,28 +2203,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="3" t="n">
+      <c r="B53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="3" t="n">
         <v>47896</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K53" s="3" t="n">
         <v>695</v>
       </c>
     </row>
@@ -2222,28 +2234,28 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="3" t="n">
+      <c r="B54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="2" t="n">
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="3" t="n">
         <v>6528</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="K54" s="3" t="n">
         <v>811</v>
       </c>
     </row>
@@ -2253,34 +2265,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="5" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="I55" s="5" t="n">
-        <v>0.4774560014636259</v>
-      </c>
-      <c r="J55" s="2" t="n">
+      <c r="I55" s="6" t="n">
+        <v>0.477456001463626</v>
+      </c>
+      <c r="J55" s="3" t="n">
         <v>183783</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="K55" s="3" t="n">
         <v>11462</v>
       </c>
     </row>
@@ -2290,28 +2302,28 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="2" t="n">
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr"/>
+      <c r="J56" s="3" t="n">
         <v>5473</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="K56" s="3" t="n">
         <v>2403</v>
       </c>
     </row>
@@ -2321,34 +2333,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="I57" s="5" t="n">
-        <v>0.08106606109529821</v>
-      </c>
-      <c r="J57" s="2" t="n">
+      <c r="I57" s="6" t="n">
+        <v>0.08106606109529807</v>
+      </c>
+      <c r="J57" s="3" t="n">
         <v>235441</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="K57" s="3" t="n">
         <v>18652</v>
       </c>
     </row>
@@ -2358,34 +2370,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="5" t="n">
         <v>38.1</v>
       </c>
-      <c r="I58" s="5" t="n">
-        <v>0.4142673366090833</v>
-      </c>
-      <c r="J58" s="2" t="n">
+      <c r="I58" s="6" t="n">
+        <v>0.4142673366090839</v>
+      </c>
+      <c r="J58" s="3" t="n">
         <v>248736</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="K58" s="3" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2395,28 +2407,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="3" t="n">
+      <c r="B59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="3" t="n">
         <v>11319</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="K59" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2426,28 +2438,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="3" t="n">
+      <c r="B60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="2" t="n">
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="K60" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2457,28 +2469,28 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="3" t="n">
+      <c r="B61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>1.04</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="K61" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2488,28 +2500,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="3" t="n">
+      <c r="B62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="2" t="n">
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="3" t="n">
         <v>35239</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="K62" s="3" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2519,28 +2531,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="3" t="n">
+      <c r="B63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="3" t="n">
         <v>10011</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="K63" s="3" t="n">
         <v>815</v>
       </c>
     </row>
@@ -2550,28 +2562,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="3" t="n">
+      <c r="B64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="3" t="n">
+      <c r="D64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="2" t="n">
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="3" t="n">
         <v>43112</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="K64" s="3" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2581,28 +2593,28 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="3" t="n">
+      <c r="B65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="3" t="n">
+      <c r="D65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="2" t="n">
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="3" t="n">
         <v>43112</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="K65" s="3" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2612,28 +2624,28 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="4" t="n">
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="5" t="n">
         <v>90.7</v>
       </c>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="3" t="n">
         <v>50507</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K66" s="3" t="n">
         <v>7155</v>
       </c>
     </row>
@@ -2643,28 +2655,28 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C67" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="4" t="n">
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="3" t="n">
         <v>200518</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="K67" s="3" t="n">
         <v>7678</v>
       </c>
     </row>
@@ -2674,34 +2686,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="4" t="n">
         <v>1.29</v>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="I68" s="5" t="n">
-        <v>0.0241544633916244</v>
-      </c>
-      <c r="J68" s="2" t="n">
+      <c r="I68" s="6" t="n">
+        <v>0.02415446339162438</v>
+      </c>
+      <c r="J68" s="3" t="n">
         <v>1089615</v>
       </c>
-      <c r="K68" s="2" t="n">
+      <c r="K68" s="3" t="n">
         <v>64702</v>
       </c>
     </row>
@@ -2711,28 +2723,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="3" t="n">
+      <c r="B69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="3" t="n">
         <v>21533</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="K69" s="3" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2742,34 +2754,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="4" t="n">
         <v>0.98</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="4" t="n">
         <v>1.62</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="5" t="n">
         <v>84.7</v>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>0.1303944923470493</v>
-      </c>
-      <c r="J70" s="2" t="n">
+      <c r="I70" s="6" t="n">
+        <v>0.1303944923470491</v>
+      </c>
+      <c r="J70" s="3" t="n">
         <v>288745</v>
       </c>
-      <c r="K70" s="2" t="n">
+      <c r="K70" s="3" t="n">
         <v>21673</v>
       </c>
     </row>
@@ -2779,34 +2791,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="F71" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="G71" s="3" t="n">
+      <c r="G71" s="4" t="n">
         <v>5.08</v>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="I71" s="5" t="n">
+      <c r="I71" s="6" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="3" t="n">
         <v>79458</v>
       </c>
-      <c r="K71" s="2" t="n">
+      <c r="K71" s="3" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2816,28 +2828,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="3" t="n">
+      <c r="B72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="2" t="n">
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="3" t="n">
         <v>47885</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="K72" s="3" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2847,34 +2859,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="4" t="n">
         <v>0.13</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="4" t="n">
         <v>9.68</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>89.2</v>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="I73" s="6" t="n">
         <v>0.00132463054799409</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="3" t="n">
         <v>3207</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="K73" s="3" t="n">
         <v>1358</v>
       </c>
     </row>
@@ -2884,34 +2896,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G74" s="3" t="n">
+      <c r="G74" s="4" t="n">
         <v>2.48</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="5" t="n">
         <v>70.3</v>
       </c>
-      <c r="I74" s="5" t="n">
+      <c r="I74" s="6" t="n">
         <v>0.729252497935799</v>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="3" t="n">
         <v>47636</v>
       </c>
-      <c r="K74" s="2" t="n">
+      <c r="K74" s="3" t="n">
         <v>6169</v>
       </c>
     </row>
@@ -2921,34 +2933,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="4" t="n">
         <v>1.44</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="G75" s="4" t="n">
         <v>19.1</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="5" t="n">
         <v>86.2</v>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>0.5541248070783213</v>
-      </c>
-      <c r="J75" s="2" t="n">
+      <c r="I75" s="6" t="n">
+        <v>0.5541248070783218</v>
+      </c>
+      <c r="J75" s="3" t="n">
         <v>172482</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="K75" s="3" t="n">
         <v>9151</v>
       </c>
     </row>
@@ -2958,34 +2970,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="4" t="n">
         <v>1.17</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="F76" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="G76" s="3" t="n">
+      <c r="G76" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="5" t="n">
         <v>63.9</v>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0.2740436102736469</v>
-      </c>
-      <c r="J76" s="2" t="n">
+      <c r="I76" s="6" t="n">
+        <v>0.2740436102736468</v>
+      </c>
+      <c r="J76" s="3" t="n">
         <v>673101</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="K76" s="3" t="n">
         <v>45112</v>
       </c>
     </row>
@@ -2995,34 +3007,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="G77" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="5" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0.00522361300352628</v>
-      </c>
-      <c r="J77" s="2" t="n">
+      <c r="I77" s="6" t="n">
+        <v>0.005223613003526282</v>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>1911711</v>
       </c>
-      <c r="K77" s="2" t="n">
+      <c r="K77" s="3" t="n">
         <v>47035</v>
       </c>
     </row>
@@ -3032,34 +3044,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="G78" s="3" t="n">
+      <c r="G78" s="4" t="n">
         <v>2.02</v>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="H78" s="5" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="I78" s="6" t="n">
         <v>0.1137710197915857</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="3" t="n">
         <v>253195</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="K78" s="3" t="n">
         <v>12727</v>
       </c>
     </row>
@@ -3069,34 +3081,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="5" t="n">
         <v>83.3</v>
       </c>
-      <c r="I79" s="5" t="n">
-        <v>0.1182255463777411</v>
-      </c>
-      <c r="J79" s="2" t="n">
+      <c r="I79" s="6" t="n">
+        <v>0.118225546377741</v>
+      </c>
+      <c r="J79" s="3" t="n">
         <v>688143</v>
       </c>
-      <c r="K79" s="2" t="n">
+      <c r="K79" s="3" t="n">
         <v>33749</v>
       </c>
     </row>
@@ -3106,34 +3118,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="D80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="3" t="n">
+      <c r="D80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="G80" s="3" t="n">
+      <c r="G80" s="4" t="n">
         <v>12.86</v>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H80" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="I80" s="6" t="n">
         <v>0.257220017732754</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="3" t="n">
         <v>201324</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="K80" s="3" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3143,34 +3155,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="4" t="n">
         <v>2.01</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G81" s="3" t="n">
+      <c r="G81" s="4" t="n">
         <v>159.52</v>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="5" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="I81" s="6" t="n">
         <v>0.6751776574754227</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="3" t="n">
         <v>247791</v>
       </c>
-      <c r="K81" s="2" t="n">
+      <c r="K81" s="3" t="n">
         <v>29373</v>
       </c>
     </row>
@@ -3180,28 +3192,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="3" t="n">
+      <c r="B82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="4" t="n">
         <v>1.64</v>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="2" t="n">
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="3" t="n">
         <v>2611</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="K82" s="3" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3211,28 +3223,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="D83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3" t="n">
+      <c r="D83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="4" t="n">
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="5" t="n">
         <v>57.1</v>
       </c>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="2" t="n">
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="3" t="n">
         <v>44462</v>
       </c>
-      <c r="K83" s="2" t="n">
+      <c r="K83" s="3" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3242,34 +3254,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="4" t="n">
         <v>2.45</v>
       </c>
-      <c r="F84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3" t="n">
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="I84" s="5" t="n">
+      <c r="I84" s="6" t="n">
         <v>0.1814798483236068</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="3" t="n">
         <v>3460</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="K84" s="3" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3279,28 +3291,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="3" t="n">
+      <c r="B85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="F85" s="3" t="inlineStr"/>
-      <c r="G85" s="3" t="inlineStr"/>
-      <c r="H85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="2" t="n">
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr"/>
+      <c r="J85" s="3" t="n">
         <v>58279</v>
       </c>
-      <c r="K85" s="2" t="n">
+      <c r="K85" s="3" t="n">
         <v>642</v>
       </c>
     </row>
@@ -3310,28 +3322,28 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C86" s="3" t="n">
+      <c r="C86" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E86" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="4" t="n">
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="3" t="n">
         <v>719</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="K86" s="3" t="n">
         <v>245</v>
       </c>
     </row>
@@ -3341,34 +3353,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="4" t="n">
         <v>2.23</v>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="F87" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="G87" s="3" t="n">
+      <c r="G87" s="4" t="n">
         <v>5.24</v>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="5" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="I87" s="5" t="n">
-        <v>0.081214709783867</v>
-      </c>
-      <c r="J87" s="2" t="n">
+      <c r="I87" s="6" t="n">
+        <v>0.08121470978386684</v>
+      </c>
+      <c r="J87" s="3" t="n">
         <v>873126</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="K87" s="3" t="n">
         <v>56254</v>
       </c>
     </row>
@@ -3378,28 +3390,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="3" t="n">
+      <c r="B88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="2" t="n">
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr"/>
+      <c r="J88" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="K88" s="2" t="n">
+      <c r="K88" s="3" t="n">
         <v>130</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_prostate_cancer_excluding_aggressive_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,28 +514,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>102</v>
       </c>
     </row>
@@ -557,28 +545,28 @@
           <t>natto</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>140</v>
       </c>
     </row>
@@ -588,28 +576,28 @@
           <t>papaya</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -619,28 +607,28 @@
           <t>genistein</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.37</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>43907</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>440</v>
       </c>
     </row>
@@ -650,28 +638,28 @@
           <t>early_time_restricted_eating</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -681,34 +669,34 @@
           <t>soy</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="4" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0.1010785350953813</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="I7" s="5" t="n">
+        <v>0.1010785350953814</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>85059</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>5399</v>
       </c>
     </row>
@@ -718,28 +706,28 @@
           <t>low_fat_diet</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>1170</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>390</v>
       </c>
     </row>
@@ -749,34 +737,34 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="4" t="n">
         <v>76.2</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="5" t="n">
         <v>0.2620449311218541</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="2" t="n">
         <v>49170</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>1463</v>
       </c>
     </row>
@@ -786,28 +774,28 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>1623</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>677</v>
       </c>
     </row>
@@ -817,28 +805,28 @@
           <t>vitamin_k</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="3" t="n">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -848,28 +836,28 @@
           <t>vitamin_k2</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -879,28 +867,28 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>971</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>433</v>
       </c>
     </row>
@@ -910,28 +898,28 @@
           <t>vegan_diet</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="3" t="n">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>26346</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>1079</v>
       </c>
     </row>
@@ -941,28 +929,28 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="5" t="n">
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="3" t="n">
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
         <v>57649</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>6553</v>
       </c>
     </row>
@@ -972,34 +960,34 @@
           <t>garlic</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>265.07</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="5" t="n">
         <v>0.2044018200861738</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="2" t="n">
         <v>36604</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1009,28 +997,28 @@
           <t>vegetarian_diet</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="3" t="n">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>217937</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>9501</v>
       </c>
     </row>
@@ -1040,34 +1028,34 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="4" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>2.045420729252859e-05</v>
-      </c>
-      <c r="J18" s="3" t="n">
+      <c r="I18" s="5" t="n">
+        <v>2.045420729252854e-05</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>1057923</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>67108</v>
       </c>
     </row>
@@ -1077,28 +1065,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="n">
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>652</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>244</v>
       </c>
     </row>
@@ -1108,28 +1096,28 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="n">
+      <c r="B20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1139,34 +1127,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="4" t="n">
         <v>85.8</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>0.08361480732068771</v>
-      </c>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="5" t="n">
+        <v>0.08361480732068802</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>264478</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>15275</v>
       </c>
     </row>
@@ -1176,28 +1164,28 @@
           <t>iodine</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="3" t="n">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>656</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>328</v>
       </c>
     </row>
@@ -1207,28 +1195,28 @@
           <t>time_restricted_eating</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="n">
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="3" t="n">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>607</v>
       </c>
     </row>
@@ -1238,34 +1226,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="4" t="n">
         <v>67.2</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <v>0.06273674991285325</v>
-      </c>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="5" t="n">
+        <v>0.0627367499128533</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>93912</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>4718</v>
       </c>
     </row>
@@ -1275,28 +1263,28 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="n">
+      <c r="B25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="3" t="n">
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
         <v>2745</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1306,28 +1294,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>2745</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1337,28 +1325,28 @@
           <t>mushrooms</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>36499</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>1204</v>
       </c>
     </row>
@@ -1368,34 +1356,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>0.8930041904516861</v>
-      </c>
-      <c r="J28" s="3" t="n">
+      <c r="I28" s="5" t="n">
+        <v>0.8930041904516864</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>68446</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>7637</v>
       </c>
     </row>
@@ -1405,34 +1393,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="4" t="n">
         <v>69.5</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>0.0749554992913304</v>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="n">
+        <v>0.07495549929133036</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>282888</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>22602</v>
       </c>
     </row>
@@ -1442,34 +1430,34 @@
           <t>legumes</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="4" t="n">
         <v>62.4</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <v>0.006170430008920973</v>
-      </c>
-      <c r="J30" s="3" t="n">
+      <c r="I30" s="5" t="n">
+        <v>0.00617043000892098</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>1155076</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>79072</v>
       </c>
     </row>
@@ -1479,34 +1467,34 @@
           <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>0.188399637329524</v>
-      </c>
-      <c r="J31" s="3" t="n">
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.1883996373295245</v>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>80888</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>10851</v>
       </c>
     </row>
@@ -1516,34 +1504,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0.2443574036478493</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.2443574036478494</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>70879</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>7656</v>
       </c>
     </row>
@@ -1553,34 +1541,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="I33" s="6" t="n">
-        <v>0.9409244606491105</v>
-      </c>
-      <c r="J33" s="3" t="n">
+      <c r="I33" s="5" t="n">
+        <v>0.94092446064911</v>
+      </c>
+      <c r="J33" s="2" t="n">
         <v>65550</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>6813</v>
       </c>
     </row>
@@ -1590,28 +1578,28 @@
           <t>plant_based_diet</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
         <v>211318</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>24516</v>
       </c>
     </row>
@@ -1621,28 +1609,28 @@
           <t>caffeine</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>46667</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -1652,28 +1640,28 @@
           <t>ginseng</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="n">
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1683,34 +1671,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="n">
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>0.77</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="4" t="n">
         <v>42.9</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>0.07744276379719461</v>
-      </c>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="n">
+        <v>0.0774427637971946</v>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>972077</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>64899</v>
       </c>
     </row>
@@ -1720,28 +1708,28 @@
           <t>ginkgo_biloba</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>38308</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>1665</v>
       </c>
     </row>
@@ -1751,28 +1739,28 @@
           <t>coenzyme_q10</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="n">
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1782,28 +1770,28 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>430507</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>7761</v>
       </c>
     </row>
@@ -1813,28 +1801,28 @@
           <t>mediterranean_diet</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4" t="n">
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="3" t="n">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
         <v>47867</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -1844,34 +1832,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="4" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="I42" s="6" t="n">
-        <v>0.116278835132563</v>
-      </c>
-      <c r="J42" s="3" t="n">
+      <c r="I42" s="5" t="n">
+        <v>0.1162788351325633</v>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>270107</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>13301</v>
       </c>
     </row>
@@ -1881,28 +1869,28 @@
           <t>dash_diet</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="n">
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>72784</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>1408</v>
       </c>
     </row>
@@ -1912,28 +1900,28 @@
           <t>fish_oil</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="n">
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -1943,28 +1931,28 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="n">
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="3" t="n">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
         <v>150671</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>14238</v>
       </c>
     </row>
@@ -1974,28 +1962,28 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4" t="n">
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>159482</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>17349</v>
       </c>
     </row>
@@ -2005,28 +1993,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="3" t="n">
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
         <v>109557</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>3064</v>
       </c>
     </row>
@@ -2036,34 +2024,34 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="n">
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
         <v>0.8121269612161565</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="J48" s="2" t="n">
         <v>900752</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>53381</v>
       </c>
     </row>
@@ -2073,28 +2061,28 @@
           <t>docosapentaenoic_acid_omega_3</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="4" t="n">
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="3" t="n">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2104,34 +2092,34 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="4" t="n">
+      <c r="C50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H50" s="4" t="n">
         <v>76.5</v>
       </c>
-      <c r="I50" s="6" t="n">
-        <v>0.6025874689662087</v>
-      </c>
-      <c r="J50" s="3" t="n">
+      <c r="I50" s="5" t="n">
+        <v>0.6025874689662086</v>
+      </c>
+      <c r="J50" s="2" t="n">
         <v>271067</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>17634</v>
       </c>
     </row>
@@ -2141,28 +2129,28 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4" t="n">
+      <c r="B51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="3" t="n">
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2172,28 +2160,28 @@
           <t>gondoic_acid</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4" t="n">
+      <c r="B52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="3" t="n">
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
         <v>142239</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>7036</v>
       </c>
     </row>
@@ -2203,28 +2191,28 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="4" t="n">
+      <c r="B53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="3" t="n">
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="2" t="n">
         <v>47896</v>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" s="2" t="n">
         <v>695</v>
       </c>
     </row>
@@ -2234,28 +2222,28 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="4" t="n">
+      <c r="B54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="3" t="n">
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="2" t="n">
         <v>6528</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="2" t="n">
         <v>811</v>
       </c>
     </row>
@@ -2265,34 +2253,34 @@
           <t>iron</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="C55" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="4" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="I55" s="6" t="n">
-        <v>0.477456001463626</v>
-      </c>
-      <c r="J55" s="3" t="n">
+      <c r="I55" s="5" t="n">
+        <v>0.4774560014636261</v>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>183783</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" s="2" t="n">
         <v>11462</v>
       </c>
     </row>
@@ -2302,28 +2290,28 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="3" t="n">
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="2" t="n">
         <v>5473</v>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" s="2" t="n">
         <v>2403</v>
       </c>
     </row>
@@ -2333,34 +2321,34 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="4" t="n">
         <v>43.6</v>
       </c>
-      <c r="I57" s="6" t="n">
-        <v>0.08106606109529807</v>
-      </c>
-      <c r="J57" s="3" t="n">
+      <c r="I57" s="5" t="n">
+        <v>0.08106606109529818</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>235441</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" s="2" t="n">
         <v>18652</v>
       </c>
     </row>
@@ -2370,34 +2358,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="H58" s="5" t="n">
+      <c r="H58" s="4" t="n">
         <v>38.1</v>
       </c>
-      <c r="I58" s="6" t="n">
-        <v>0.4142673366090839</v>
-      </c>
-      <c r="J58" s="3" t="n">
+      <c r="I58" s="5" t="n">
+        <v>0.4142673366090832</v>
+      </c>
+      <c r="J58" s="2" t="n">
         <v>248736</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="2" t="n">
         <v>13760</v>
       </c>
     </row>
@@ -2407,28 +2395,28 @@
           <t>vitamin_k1</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="4" t="n">
+      <c r="B59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="3" t="n">
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
         <v>11319</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" s="2" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2438,28 +2426,28 @@
           <t>saw_palmetto</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4" t="n">
+      <c r="B60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="3" t="n">
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2469,28 +2457,28 @@
           <t>glucosamine</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="n">
+      <c r="B61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="3" t="n">
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2500,28 +2488,28 @@
           <t>chondroitin</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4" t="n">
+      <c r="B62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr"/>
-      <c r="J62" s="3" t="n">
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="2" t="n">
         <v>35239</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" s="2" t="n">
         <v>1602</v>
       </c>
     </row>
@@ -2531,28 +2519,28 @@
           <t>mineral_supplements</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="4" t="n">
+      <c r="B63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="3" t="n">
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="2" t="n">
         <v>10011</v>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="K63" s="2" t="n">
         <v>815</v>
       </c>
     </row>
@@ -2562,28 +2550,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="4" t="n">
+      <c r="B64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="4" t="n">
+      <c r="D64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="3" t="n">
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="2" t="n">
         <v>43112</v>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="K64" s="2" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2593,28 +2581,28 @@
           <t>magnesium</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="4" t="n">
+      <c r="B65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="n">
         <v>1.06</v>
       </c>
-      <c r="D65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="4" t="n">
+      <c r="D65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
-      <c r="H65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="3" t="n">
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="2" t="n">
         <v>43112</v>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="K65" s="2" t="n">
         <v>6058</v>
       </c>
     </row>
@@ -2624,28 +2612,28 @@
           <t>antioxidants</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="5" t="n">
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
         <v>90.7</v>
       </c>
-      <c r="I66" s="6" t="inlineStr"/>
-      <c r="J66" s="3" t="n">
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="2" t="n">
         <v>50507</v>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="K66" s="2" t="n">
         <v>7155</v>
       </c>
     </row>
@@ -2655,28 +2643,28 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C67" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="5" t="n">
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
         <v>44.6</v>
       </c>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="3" t="n">
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="2" t="n">
         <v>200518</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" s="2" t="n">
         <v>7678</v>
       </c>
     </row>
@@ -2686,34 +2674,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="H68" s="5" t="n">
+      <c r="H68" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="I68" s="6" t="n">
-        <v>0.02415446339162438</v>
-      </c>
-      <c r="J68" s="3" t="n">
+      <c r="I68" s="5" t="n">
+        <v>0.02415446339162439</v>
+      </c>
+      <c r="J68" s="2" t="n">
         <v>1089615</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="2" t="n">
         <v>64702</v>
       </c>
     </row>
@@ -2723,28 +2711,28 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="4" t="n">
+      <c r="B69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="n">
         <v>1.09</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="3" t="n">
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="2" t="n">
         <v>21533</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="2" t="n">
         <v>291</v>
       </c>
     </row>
@@ -2754,34 +2742,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="4" t="n">
         <v>84.7</v>
       </c>
-      <c r="I70" s="6" t="n">
-        <v>0.1303944923470491</v>
-      </c>
-      <c r="J70" s="3" t="n">
+      <c r="I70" s="5" t="n">
+        <v>0.1303944923470489</v>
+      </c>
+      <c r="J70" s="2" t="n">
         <v>288745</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="2" t="n">
         <v>21673</v>
       </c>
     </row>
@@ -2791,34 +2779,34 @@
           <t>whole_grain_intake</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="C71" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="3" t="n">
         <v>0.97</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="H71" s="5" t="n">
+      <c r="H71" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" s="5" t="n">
         <v>0.1158775811071888</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="J71" s="2" t="n">
         <v>79458</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="2" t="n">
         <v>7209</v>
       </c>
     </row>
@@ -2828,28 +2816,28 @@
           <t>phosphorus</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="4" t="n">
+      <c r="B72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr"/>
-      <c r="H72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="3" t="n">
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="2" t="n">
         <v>47885</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="2" t="n">
         <v>5861</v>
       </c>
     </row>
@@ -2859,34 +2847,34 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C73" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="3" t="n">
         <v>1.99</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="3" t="n">
         <v>9.68</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="4" t="n">
         <v>89.2</v>
       </c>
-      <c r="I73" s="6" t="n">
-        <v>0.00132463054799409</v>
-      </c>
-      <c r="J73" s="3" t="n">
+      <c r="I73" s="5" t="n">
+        <v>0.001324630547994084</v>
+      </c>
+      <c r="J73" s="2" t="n">
         <v>3207</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="2" t="n">
         <v>1358</v>
       </c>
     </row>
@@ -2896,34 +2884,34 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="4" t="n">
         <v>70.3</v>
       </c>
-      <c r="I74" s="6" t="n">
-        <v>0.729252497935799</v>
-      </c>
-      <c r="J74" s="3" t="n">
+      <c r="I74" s="5" t="n">
+        <v>0.7292524979357997</v>
+      </c>
+      <c r="J74" s="2" t="n">
         <v>47636</v>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="K74" s="2" t="n">
         <v>6169</v>
       </c>
     </row>
@@ -2933,34 +2921,34 @@
           <t>alpha_linolenic_acid</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C75" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="3" t="n">
         <v>1.44</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="4" t="n">
         <v>86.2</v>
       </c>
-      <c r="I75" s="6" t="n">
-        <v>0.5541248070783218</v>
-      </c>
-      <c r="J75" s="3" t="n">
+      <c r="I75" s="5" t="n">
+        <v>0.5541248070783213</v>
+      </c>
+      <c r="J75" s="2" t="n">
         <v>172482</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" s="2" t="n">
         <v>9151</v>
       </c>
     </row>
@@ -2970,34 +2958,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="4" t="n">
         <v>63.9</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <v>0.2740436102736468</v>
-      </c>
-      <c r="J76" s="3" t="n">
+      <c r="I76" s="5" t="n">
+        <v>0.2740436102736469</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>673101</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K76" s="2" t="n">
         <v>45112</v>
       </c>
     </row>
@@ -3007,34 +2995,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C77" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="3" t="n">
         <v>1.66</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="4" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="I77" s="6" t="n">
+      <c r="I77" s="5" t="n">
         <v>0.005223613003526282</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="J77" s="2" t="n">
         <v>1911711</v>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="K77" s="2" t="n">
         <v>47035</v>
       </c>
     </row>
@@ -3044,34 +3032,34 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="4" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="I78" s="6" t="n">
+      <c r="I78" s="5" t="n">
         <v>0.1137710197915857</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="J78" s="2" t="n">
         <v>253195</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" s="2" t="n">
         <v>12727</v>
       </c>
     </row>
@@ -3081,34 +3069,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C79" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="I79" s="6" t="n">
-        <v>0.118225546377741</v>
-      </c>
-      <c r="J79" s="3" t="n">
+      <c r="I79" s="5" t="n">
+        <v>0.1182255463777411</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>688143</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K79" s="2" t="n">
         <v>33749</v>
       </c>
     </row>
@@ -3118,34 +3106,34 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="4" t="n">
+      <c r="D80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="4" t="n">
         <v>50.3</v>
       </c>
-      <c r="I80" s="6" t="n">
-        <v>0.257220017732754</v>
-      </c>
-      <c r="J80" s="3" t="n">
+      <c r="I80" s="5" t="n">
+        <v>0.2572200177327541</v>
+      </c>
+      <c r="J80" s="2" t="n">
         <v>201324</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="K80" s="2" t="n">
         <v>7680</v>
       </c>
     </row>
@@ -3155,34 +3143,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="3" t="n">
         <v>159.52</v>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="I81" s="6" t="n">
-        <v>0.6751776574754227</v>
-      </c>
-      <c r="J81" s="3" t="n">
+      <c r="I81" s="5" t="n">
+        <v>0.6751776574754228</v>
+      </c>
+      <c r="J81" s="2" t="n">
         <v>247791</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" s="2" t="n">
         <v>29373</v>
       </c>
     </row>
@@ -3192,28 +3180,28 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="4" t="n">
+      <c r="B82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="3" t="n">
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
         <v>2611</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="2" t="n">
         <v>1499</v>
       </c>
     </row>
@@ -3223,28 +3211,28 @@
           <t>western_pattern_diet</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C83" s="4" t="n">
+      <c r="C83" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="4" t="n">
+      <c r="D83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="5" t="n">
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="I83" s="6" t="inlineStr"/>
-      <c r="J83" s="3" t="n">
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="2" t="n">
         <v>44462</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" s="2" t="n">
         <v>1702</v>
       </c>
     </row>
@@ -3254,34 +3242,34 @@
           <t>fermented_foods</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="F84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4" t="n">
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
         <v>664.3099999999999</v>
       </c>
-      <c r="H84" s="5" t="n">
+      <c r="H84" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="I84" s="6" t="n">
-        <v>0.1814798483236068</v>
-      </c>
-      <c r="J84" s="3" t="n">
+      <c r="I84" s="5" t="n">
+        <v>0.1814798483236069</v>
+      </c>
+      <c r="J84" s="2" t="n">
         <v>3460</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="K84" s="2" t="n">
         <v>339</v>
       </c>
     </row>
@@ -3291,28 +3279,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="n">
+      <c r="B85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="3" t="n">
         <v>2.19</v>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr"/>
-      <c r="H85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr"/>
-      <c r="J85" s="3" t="n">
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="2" t="n">
         <v>58279</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" s="2" t="n">
         <v>642</v>
       </c>
     </row>
@@ -3322,28 +3310,28 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C86" s="4" t="n">
+      <c r="C86" s="3" t="n">
         <v>1.47</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="3" t="n">
         <v>1.02</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="5" t="n">
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="3" t="n">
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
         <v>719</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="K86" s="2" t="n">
         <v>245</v>
       </c>
     </row>
@@ -3353,34 +3341,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="3" t="n">
         <v>5.24</v>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="4" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="I87" s="6" t="n">
-        <v>0.08121470978386684</v>
-      </c>
-      <c r="J87" s="3" t="n">
+      <c r="I87" s="5" t="n">
+        <v>0.08121470978386697</v>
+      </c>
+      <c r="J87" s="2" t="n">
         <v>873126</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="K87" s="2" t="n">
         <v>56254</v>
       </c>
     </row>
@@ -3390,28 +3378,28 @@
           <t>pickled_vegetables</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="4" t="n">
+      <c r="B88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="3" t="n">
         <v>4.58</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="3" t="n">
         <v>5.94</v>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr"/>
-      <c r="J88" s="3" t="n">
+      <c r="F88" s="3" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" s="2" t="n">
         <v>130</v>
       </c>
     </row>
